--- a/pipeline_output/JH_2W_H&M.xlsx
+++ b/pipeline_output/JH_2W_H&M.xlsx
@@ -736,12 +736,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1361,12 +1361,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1732,12 +1732,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3333,12 +3333,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -3567,12 +3567,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -4426,12 +4426,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -6144,12 +6144,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -6378,12 +6378,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="AQ48" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>750</t>
         </is>
       </c>
     </row>
@@ -6505,12 +6505,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -6632,12 +6632,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -7003,12 +7003,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -7130,12 +7130,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -7257,12 +7257,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -7745,12 +7745,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1000</t>
         </is>
       </c>
     </row>
@@ -7999,12 +7999,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -8380,12 +8380,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -8634,12 +8634,12 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -8761,12 +8761,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -9015,12 +9015,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -9132,12 +9132,12 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -9366,12 +9366,12 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -9834,12 +9834,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -9951,12 +9951,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -10185,12 +10185,12 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -10302,12 +10302,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -10419,12 +10419,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -10653,12 +10653,12 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -10770,12 +10770,12 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
